--- a/Storage/SampleData/CommonConfig.xlsx
+++ b/Storage/SampleData/CommonConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCA553D-7ADD-4A48-9561-2622CEC607A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE101BD3-737C-4B1B-8BD6-9FE3CDFCD0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16305" yWindow="16305" windowWidth="16410" windowHeight="9975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16200" yWindow="1995" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CommonConfig" sheetId="1" r:id="rId1"/>

--- a/Storage/SampleData/CommonConfig.xlsx
+++ b/Storage/SampleData/CommonConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE101BD3-737C-4B1B-8BD6-9FE3CDFCD0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5684CBE3-2064-4B67-9E00-19C08B25D5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16200" yWindow="1995" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CommonConfig" sheetId="1" r:id="rId1"/>
@@ -71,10 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>승리하기 위해 필요한 승점 에너지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>max_unit_size_to_field</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -104,6 +100,10 @@
   </si>
   <si>
     <t>최대 손패 사이즈 (이하)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>승리하기 위해 필요한 승점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -524,51 +524,51 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Storage/SampleData/CommonConfig.xlsx
+++ b/Storage/SampleData/CommonConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5684CBE3-2064-4B67-9E00-19C08B25D5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2882C3F-9ED3-41BA-AEA5-01154243E121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -104,6 +104,22 @@
   </si>
   <si>
     <t>승리하기 위해 필요한 승점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>room_session_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 방 유지 시간 (ms초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choose_wait_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 대기 시간 (ms초)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -181,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E2719ABB-62B7-41DC-8FF6-A3988B691283}" name="CommonConfig" displayName="CommonConfig" ref="A2:C11" totalsRowShown="0">
-  <autoFilter ref="A2:C11" xr:uid="{E2719ABB-62B7-41DC-8FF6-A3988B691283}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E2719ABB-62B7-41DC-8FF6-A3988B691283}" name="CommonConfig" displayName="CommonConfig" ref="A2:C13" totalsRowShown="0">
+  <autoFilter ref="A2:C13" xr:uid="{E2719ABB-62B7-41DC-8FF6-A3988B691283}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1EFB0E40-FCB9-4E2B-931E-5C2FE6377C40}" name="Name"/>
     <tableColumn id="2" xr3:uid="{D87CD009-B99B-43FB-902E-215BEE534F1B}" name="Value"/>
@@ -455,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C11"/>
+  <dimension ref="A2:C13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.875" bestFit="1" customWidth="1"/>
@@ -571,6 +587,28 @@
         <v>18</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>60000</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>2000</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
